--- a/application/plugins/Reports_summary_sell_profit/views/Reports_summary_sell_profit.xlsx
+++ b/application/plugins/Reports_summary_sell_profit/views/Reports_summary_sell_profit.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Wamp.NET\sites\isell\isell\application\plugins\Reports_summary_sell_profit\views\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -19,10 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
-  <si>
-    <t>Развернутый анализ продаж и прибыли</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t>Исходные данные</t>
   </si>
@@ -81,9 +83,6 @@
     <t>{$v-&gt;input-&gt;path_include}</t>
   </si>
   <si>
-    <t>Итоги анализа продаж и прибыли</t>
-  </si>
-  <si>
     <t>Кол-во</t>
   </si>
   <si>
@@ -166,27 +165,28 @@
   </si>
   <si>
     <t>{$v-&gt;rows[]-&gt;net_prod_sum}</t>
+  </si>
+  <si>
+    <t>Группа</t>
+  </si>
+  <si>
+    <t>Подробный отчет</t>
+  </si>
+  <si>
+    <t>Анализ продаж и прибыли</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -227,11 +227,12 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="18"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -272,7 +273,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -281,21 +282,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -303,62 +289,6 @@
         <color auto="1"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -466,107 +396,267 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Процентный" xfId="1" builtinId="5"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -642,14 +732,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -687,9 +780,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -724,7 +817,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -759,7 +852,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -933,290 +1026,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="9.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
+      <c r="A3" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="18"/>
+      <c r="A4" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="30"/>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="18"/>
+      <c r="A5" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="30"/>
       <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="18"/>
+      <c r="A6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="30"/>
       <c r="C6" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="18"/>
+      <c r="A7" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="30"/>
       <c r="C7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="18"/>
+      <c r="A8" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="30"/>
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="18"/>
+      <c r="A9" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="30"/>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="18"/>
+      <c r="A10" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="32"/>
       <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="1" t="s">
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:10" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C12" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="37"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="38"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:10" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="D14" s="24" t="s">
+      <c r="F13" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="33"/>
+      <c r="J13" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="34"/>
+      <c r="J14" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="2" t="s">
+      <c r="C15" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="29"/>
+      <c r="E15" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="49"/>
+      <c r="J15" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="22"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:10" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="52"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I20" s="45"/>
+      <c r="J20" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D16" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D17" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" s="8" t="s">
+    </row>
+    <row r="21" spans="1:10" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="24" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="31" t="s">
+      <c r="C21" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="32"/>
-      <c r="J19" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13" t="s">
+      <c r="D21" s="44"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="G21" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="13" t="s">
+      <c r="H21" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" s="41"/>
+    </row>
+    <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="B22" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H20" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J20" s="25"/>
-    </row>
-    <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="C22" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="D22" s="43"/>
+      <c r="E22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="F22" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="7" t="s">
+      <c r="G22" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="H22" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="17" t="s">
+      <c r="I22" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="J22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I21" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="9"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="11"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="J19:J20"/>
+  <mergeCells count="28">
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="C12:J12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D14:J14"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
